--- a/china-coal/数据源/中煤能源_业务追踪数据.xlsx
+++ b/china-coal/数据源/中煤能源_业务追踪数据.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现金流量表(年度)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标(季度)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标(年度)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务表现" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +68,17 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +92,11 @@
     </fill>
     <fill>
       <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -117,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -155,6 +170,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4476,4 +4498,1057 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15" customWidth="1" style="3" min="2" max="2"/>
+    <col width="15" customWidth="1" style="3" min="3" max="3"/>
+    <col width="15" customWidth="1" style="3" min="4" max="4"/>
+    <col width="15" customWidth="1" style="3" min="5" max="5"/>
+    <col width="15" customWidth="1" style="3" min="6" max="6"/>
+    <col width="15" customWidth="1" style="3" min="7" max="7"/>
+    <col width="15" customWidth="1" style="3" min="8" max="8"/>
+    <col width="15" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15" customWidth="1" style="3" min="10" max="10"/>
+    <col width="15" customWidth="1" style="3" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>卡片4·财务表现（合并口径·财报来源·单位:亿元/%；季度值为真实单季，已做累计还原）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>报告日</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>期间</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>营业收入(亿元)</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>归母净利润(亿元)</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>经营现金流净额(亿元)</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>EPS基本(元)</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>每股净资产(元)</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>资产负债率(%)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>归母净利率(%)</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>ROE累计(%)</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>分红率(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>20200331</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>275.2</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K4" s="18" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>20200630</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K5" s="18" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>20200930</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>388.51</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>20201231</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>1409.65</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>226.32</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>20210331</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>462.36</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>20210630</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>559.4299999999999</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>144.03</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>20210930</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>653.9299999999999</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>120.72</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>20211231</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>2398.28</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>137.39</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>480.97</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="K11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>20220331</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>617.3</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="K12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>20220630</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>563.09</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="K13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>20220930</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>573.0599999999999</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>176.96</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="K14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>20221231</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>2205.77</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>182.59</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>436.34</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="K15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>20230331</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>591.58</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>110.98</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="K16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>20230630</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>501.99</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>20230930</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>468.52</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>20231231</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1929.69</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>195.34</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>429.65</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="K19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>20240331</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>453.94</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>20240630</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>475.9</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>20240930</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>474.28</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>108.67</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>20241231</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1893.96</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>192.86</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="K23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>20250331</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>383.91</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>20250630</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>20250930</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>361.37</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>134.39</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>20251231</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1480.57</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>178.84</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>297.92</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="K27" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>389.47</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K29" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>